--- a/artfynd/A 49307-2025 artfynd.xlsx
+++ b/artfynd/A 49307-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127631564</v>
+        <v>127631573</v>
       </c>
       <c r="B2" t="n">
-        <v>78787</v>
+        <v>81312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>364779</v>
+        <v>364909</v>
       </c>
       <c r="R2" t="n">
-        <v>6757608</v>
+        <v>6757965</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127631565</v>
+        <v>127631566</v>
       </c>
       <c r="B3" t="n">
-        <v>78435</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>364819</v>
+        <v>364823</v>
       </c>
       <c r="R3" t="n">
         <v>6757794</v>
@@ -877,11 +877,6 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>äldre tallskog</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -899,14 +894,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127631581</v>
+        <v>127631568</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -934,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>364968</v>
+        <v>364779</v>
       </c>
       <c r="R4" t="n">
-        <v>6757829</v>
+        <v>6757916</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,7 +983,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>äldre tallskog på lavrik mark</t>
+          <t>äldre tallskog</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1011,40 +1006,35 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127631574</v>
+        <v>127631575</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mellan väg 62 och Gåstjärnarna, Vrm</t>
@@ -1110,7 +1100,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>torrtall</t>
+          <t>tallar</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1128,50 +1118,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127631567</v>
+        <v>127631581</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mellan väg 62 och Gåstjärnarna, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>364772</v>
+        <v>364968</v>
       </c>
       <c r="R6" t="n">
-        <v>6757871</v>
+        <v>6757829</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1222,12 +1207,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>äldre tallskog</t>
+          <t>äldre tallskog på lavrik mark</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>torrtall</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1245,50 +1230,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127631569</v>
+        <v>127631583</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mellan väg 62 och Gåstjärnarna, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>364852</v>
+        <v>364908</v>
       </c>
       <c r="R7" t="n">
-        <v>6758030</v>
+        <v>6757747</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1339,12 +1319,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>äldre tallskog</t>
+          <t>äldre tallskog på lavrik mark</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>torrtall</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1362,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127631571</v>
+        <v>127631565</v>
       </c>
       <c r="B8" t="n">
-        <v>79647</v>
+        <v>78730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,21 +1353,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>364889</v>
+        <v>364819</v>
       </c>
       <c r="R8" t="n">
-        <v>6758038</v>
+        <v>6757794</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1451,7 +1431,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>äldre tallskog på lavrik mark</t>
+          <t>äldre tallskog</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1474,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127631579</v>
+        <v>127631572</v>
       </c>
       <c r="B9" t="n">
-        <v>78787</v>
+        <v>78730</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,21 +1465,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>364877</v>
+        <v>364904</v>
       </c>
       <c r="R9" t="n">
-        <v>6757791</v>
+        <v>6758032</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1568,7 +1548,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>silverstubbe</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1586,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127631572</v>
+        <v>127631564</v>
       </c>
       <c r="B10" t="n">
-        <v>78435</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,21 +1577,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>364904</v>
+        <v>364779</v>
       </c>
       <c r="R10" t="n">
-        <v>6758032</v>
+        <v>6757608</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1680,7 +1660,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>silverstubbe</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1698,50 +1678,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127631585</v>
+        <v>127631579</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Mellan väg 62 och Gåstjärnarna, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>364842</v>
+        <v>364877</v>
       </c>
       <c r="R11" t="n">
-        <v>6757711</v>
+        <v>6757791</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1797,7 +1772,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>torrtall</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1815,32 +1790,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127631566</v>
+        <v>127631571</v>
       </c>
       <c r="B12" t="n">
-        <v>92642</v>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1850,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>364823</v>
+        <v>364889</v>
       </c>
       <c r="R12" t="n">
-        <v>6757794</v>
+        <v>6758038</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1904,7 +1879,12 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>äldre tallskog</t>
+          <t>äldre tallskog på lavrik mark</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1922,45 +1902,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127631584</v>
+        <v>127631567</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>8455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mellan väg 62 och Gåstjärnarna, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>364876</v>
+        <v>364772</v>
       </c>
       <c r="R13" t="n">
-        <v>6757702</v>
+        <v>6757871</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2011,12 +1996,12 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>äldre tallskog på lavrik mark</t>
+          <t>äldre tallskog</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>torrtall</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2034,45 +2019,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127631563</v>
+        <v>127631569</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>8455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mellan väg 62 och Gåstjärnarna, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>364779</v>
+        <v>364852</v>
       </c>
       <c r="R14" t="n">
-        <v>6757608</v>
+        <v>6758030</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2123,12 +2113,12 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>äldre tallskog på lavrik mark</t>
+          <t>äldre tallskog</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>torrtall</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2146,45 +2136,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127631577</v>
+        <v>127631574</v>
       </c>
       <c r="B15" t="n">
-        <v>78012</v>
+        <v>8455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228579</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mellan väg 62 och Gåstjärnarna, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>364971</v>
+        <v>364917</v>
       </c>
       <c r="R15" t="n">
-        <v>6757865</v>
+        <v>6757996</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2235,12 +2230,12 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>sumpskogsstråk i äldre tallskog</t>
+          <t>äldre tallsumpskog</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>torrtall</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2261,7 +2256,7 @@
         <v>127631580</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,45 +2370,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127631573</v>
+        <v>127631585</v>
       </c>
       <c r="B17" t="n">
-        <v>81004</v>
+        <v>8455</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1049</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mellan väg 62 och Gåstjärnarna, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>364909</v>
+        <v>364842</v>
       </c>
       <c r="R17" t="n">
-        <v>6757965</v>
+        <v>6757711</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>torrtall</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127631575</v>
+        <v>127631577</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>78339</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2498,21 +2498,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>364917</v>
+        <v>364971</v>
       </c>
       <c r="R18" t="n">
-        <v>6757996</v>
+        <v>6757865</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2576,12 +2576,12 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>äldre tallsumpskog</t>
+          <t>sumpskogsstråk i äldre tallskog</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>tallar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127631578</v>
+        <v>127631563</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>79085</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>364877</v>
+        <v>364779</v>
       </c>
       <c r="R19" t="n">
-        <v>6757791</v>
+        <v>6757608</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2711,10 +2711,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127631568</v>
+        <v>127631578</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>79085</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2722,21 +2722,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>364779</v>
+        <v>364877</v>
       </c>
       <c r="R20" t="n">
-        <v>6757916</v>
+        <v>6757791</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2800,12 +2800,12 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>äldre tallskog</t>
+          <t>äldre tallskog på lavrik mark</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2823,10 +2823,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127631583</v>
+        <v>127631584</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79085</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2834,21 +2834,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>364908</v>
+        <v>364876</v>
       </c>
       <c r="R21" t="n">
-        <v>6757747</v>
+        <v>6757702</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>

--- a/artfynd/A 49307-2025 artfynd.xlsx
+++ b/artfynd/A 49307-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127631573</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127631566</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127631568</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127631575</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127631581</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1339,6 +1369,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127631583</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1451,6 +1486,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127631565</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1563,6 +1603,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127631572</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1675,6 +1720,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127631564</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1787,6 +1837,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127631579</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1899,6 +1954,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127631571</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2016,6 +2076,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127631567</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2133,6 +2198,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127631569</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2250,6 +2320,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127631574</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2367,6 +2442,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127631580</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2484,6 +2564,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127631585</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2596,6 +2681,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127631577</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2708,6 +2798,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127631563</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2820,6 +2915,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127631578</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2932,8 +3032,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127631584</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>